--- a/review-tasks/1b-testcase-review/participant/testcases.xlsx
+++ b/review-tasks/1b-testcase-review/participant/testcases.xlsx
@@ -921,7 +921,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Сообщение о минимальной сумме не выводится, кнопка «Далее» активна</t>
+          <t>Под полем «Сумма» сообщение о минимальной сумме не выводится</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Сообщение о минимальной сумме не выводится, кнопка «Далее» активна</t>
+          <t>Под полем «Сумма» сообщение о минимальной сумме не выводится</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>Паспорт 4518 990112; вклад 42305810100000034561, сумма 100 000,00 ₽; счёт 40817810300000034562</t>
+          <t>Паспорт 4518 990112; вклад 42305810100000034561, сумма 100 000,00 ₽; счёт 40817810300000034562, остаток 5 000,00 ₽</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>Кнопка «Подписать» активна</t>
+          <t>В поле «Код из СМС» — 6 цифр</t>
         </is>
       </c>
     </row>
@@ -4963,7 +4963,7 @@
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Нажать кнопку в окне «Обратите внимание»</t>
+          <t>Нажать «Ок»</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>Создание клиента: возраст 14 лет</t>
+          <t>Создание клиента: граница возраста 14 лет — младше отказ, в день 14-летия создание</t>
         </is>
       </c>
       <c r="D212" s="2" t="inlineStr">
@@ -5342,7 +5342,12 @@
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Открыть карточку»</t>
+          <t>Закрыть сообщение и повторно нажать «Сохранить»</t>
+        </is>
+      </c>
+      <c r="I227" s="2" t="inlineStr">
+        <is>
+          <t>Выводится сообщение «Карточка клиента сохранена», карточка в статусе «Черновик»</t>
         </is>
       </c>
     </row>
@@ -5354,12 +5359,7 @@
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Вернуться в анкету и нажать «Отмена»</t>
-        </is>
-      </c>
-      <c r="I228" s="2" t="inlineStr">
-        <is>
-          <t>Анкета закрыта, создан черновик карточки в статусе «Черновик»</t>
+          <t>Нажать «Открыть карточку»</t>
         </is>
       </c>
     </row>

--- a/review-tasks/1b-testcase-review/participant/testcases.xlsx
+++ b/review-tasks/1b-testcase-review/participant/testcases.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Тест-кейсы" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Тест-кейсы" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q259"/>
+  <dimension ref="A1:Q260"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -774,7 +774,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Открытие вклада «Надёжный»</t>
+          <t>Отказ в открытии вклада «Надёжный» при сумме ниже минимальной</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Под полем «Сумма» выводится сообщение «Минимальная сумма для вклада «Пополняемый» — 1 000,00 ₽», кнопка «Далее» неактивна</t>
+          <t>Под полем «Сумма» выводится сообщение «Введите сумму вклада», кнопка «Далее» неактивна</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Под полем «Сумма» по-прежнему выводится сообщение «Минимальная сумма для вклада «Пополняемый» — 1 000,00 ₽», кнопка «Далее» неактивна</t>
+          <t>Под полем «Сумма» выводится сообщение «Минимальная сумма для вклада «Пополняемый» — 1 000,00 ₽», кнопка «Далее» неактивна</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Заявка подтверждена, статус заявки «Обработана»</t>
+          <t>Заявка подтверждена, статус заявки «Обработана». В продуктовом профиле клиента в блоке «Вклады» отображается вклад «Надёжный» на 1 000 000,01 ₽ в статусе «Открыт»</t>
         </is>
       </c>
     </row>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Открытие вклада клиенту с FATCA</t>
+          <t>Открытие вклада клиенту, не являющемуся налоговым резидентом США</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «Исполнена»</t>
+          <t>Заявка в статусе «Исполнена». В продуктовом профиле клиента в блоке «Вклады» отображается вклад «Пополняемый» на 50 000,00 ₽ в статусе «Открыт»</t>
         </is>
       </c>
     </row>
@@ -2174,7 +2174,7 @@
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «На подтверждении»</t>
+          <t>Заявка в статусе «Исполнена»</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
@@ -2572,544 +2572,539 @@
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «Исполнена», сообщение о подтверждении контролёром не выводится. Счёт Б в блоке «Счета» в статусе «Закрыт»</t>
+          <t>Заявка в статусе «Исполнена», сообщение о подтверждении контролёром не выводится</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Шаг 8</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>В продуктовом профиле клиента проверить статус счёта Б в блоке «Счета»</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Счёт 40817810900000023452 в статусе «Открыт»</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>900409</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие вклада</t>
         </is>
       </c>
-      <c r="C98" s="2" t="inlineStr">
+      <c r="C99" s="2" t="inlineStr">
         <is>
           <t>Закрытие вклада без текущего счёта в рублях: операция не продолжается</t>
         </is>
       </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M98" s="2" t="inlineStr">
+      <c r="M99" s="2" t="inlineStr">
         <is>
           <t>Высокий</t>
         </is>
       </c>
-      <c r="N98" s="2" t="inlineStr">
+      <c r="N99" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O98" s="2" t="inlineStr">
+      <c r="O99" s="2" t="inlineStr">
         <is>
           <t>9/21/2026 15:08:52</t>
         </is>
       </c>
-      <c r="P98" s="2" t="inlineStr">
+      <c r="P99" s="2" t="inlineStr">
         <is>
           <t>Ксения Литвинова</t>
         </is>
       </c>
-      <c r="Q98" s="2" t="inlineStr">
+      <c r="Q99" s="2" t="inlineStr">
         <is>
           <t>biq90102, deposit, negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="E99" s="2" t="inlineStr">
-        <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли финансового консультанта ТП</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>tst_fk01</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900902 «Вход в ЕФР в роли финансового консультанта»</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="E100" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
+          <t>Предусловие 1</t>
         </is>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Клиент с открытым вкладом «Пополняемый». Текущих счетов в рублях у клиента нет, есть текущий счёт в долларах США</t>
+          <t>Выполнить вход в ЕФР в роли финансового консультанта ТП</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr">
+        <is>
+          <t>tst_fk01</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900902 «Вход в ЕФР в роли финансового консультанта»</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="E101" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 3</t>
+          <t>Предусловие 2</t>
         </is>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>У клиента подключено ДБО, уровень доступа «Полный»</t>
+          <t>Клиент с открытым вкладом «Пополняемый». Текущих счетов в рублях у клиента нет, есть текущий счёт в долларах США</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="E102" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>Предусловие 3</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>У клиента подключено ДБО, уровень доступа «Полный»</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="E103" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>Напротив любого вклада клиента нажать «Показать»</t>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>Открыта детальная информация о вкладе, доступна кнопка «Операции»</t>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="E104" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Операции» и выбрать «Закрыть вклад»</t>
+          <t>Напротив вклада «Пополняемый» нажать «Показать»</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Нет счёта для перечисления средств. Откройте счёт в рублях.» с кнопками «Открыть счёт» и «Отмена»</t>
+          <t>Открыта детальная информация о вкладе, доступна кнопка «Операции»</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="E105" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Отмена»</t>
+          <t>Нажать «Операции» и выбрать «Закрыть счёт»</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>Сообщение закрыто, вклад в статусе «Закрыт»</t>
+          <t>Выводится сообщение «Нет счёта для перечисления средств. Откройте счёт в рублях.» с кнопками «Открыть счёт» и «Отмена»</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="E106" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>Повторно нажать «Операции» и выбрать «Закрыть вклад»</t>
+          <t>Нажать «Отмена»</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
         <is>
-          <t>Снова выводится сообщение об отсутствии счёта для перечисления с кнопками «Открыть счёт» и «Отмена»</t>
+          <t>Сообщение закрыто, вклад в статусе «Закрыт»</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="E107" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Открыть счёт»</t>
+          <t>Повторно нажать «Операции» и выбрать «Закрыть вклад»</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
         <is>
-          <t>Запущена операция «Открытие счёта»</t>
+          <t>Снова выводится сообщение об отсутствии счёта для перечисления с кнопками «Открыть счёт» и «Отмена»</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="E108" s="2" t="inlineStr">
         <is>
+          <t>Шаг 6</t>
+        </is>
+      </c>
+      <c r="G108" s="2" t="inlineStr">
+        <is>
+          <t>Нажать «Открыть счёт»</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>Запущена операция «Открытие счёта»</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="E109" s="2" t="inlineStr">
+        <is>
           <t>Шаг 7</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr">
         <is>
           <t>Открыть клиенту текущий счёт в рублях, вернуться к вкладу и выбрать «Операции» → «Закрыть вклад»</t>
         </is>
       </c>
-      <c r="I108" s="2" t="inlineStr">
+      <c r="I109" s="2" t="inlineStr">
         <is>
           <t>Открылась страница «Параметры закрытия», в поле «Счёт для перечисления» доступен новый счёт</t>
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>900410</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие вклада</t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>Досрочное закрытие вклада с электронным подписанием</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M109" s="2" t="inlineStr">
+      <c r="M110" s="2" t="inlineStr">
         <is>
           <t>Самый высокий</t>
         </is>
       </c>
-      <c r="N109" s="2" t="inlineStr">
+      <c r="N110" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O109" s="2" t="inlineStr">
+      <c r="O110" s="2" t="inlineStr">
         <is>
           <t>9/22/2026 09:55:20</t>
         </is>
       </c>
-      <c r="P109" s="2" t="inlineStr">
+      <c r="P110" s="2" t="inlineStr">
         <is>
           <t>Ирина Соловьёва</t>
         </is>
       </c>
-      <c r="Q109" s="2" t="inlineStr">
+      <c r="Q110" s="2" t="inlineStr">
         <is>
           <t>biq90102, deposit, dbo</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="E110" s="2" t="inlineStr">
-        <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F110" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J110" s="2" t="inlineStr">
-        <is>
-          <t>tst_oper01</t>
-        </is>
-      </c>
-      <c r="K110" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
+          <t>Предусловие 1</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Клиент от 18 лет с вкладом «Надёжный» в статусе «Открыт» и открытым текущим счётом в рублях. Вклад открыт 30 дней назад на срок 181 день</t>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
         </is>
       </c>
       <c r="J111" s="2" t="inlineStr">
         <is>
-          <t>Паспорт 4518 990112; вклад 42305810100000034561, сумма 100 000,00 ₽; счёт 40817810300000034562, остаток 5 000,00 ₽</t>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 3</t>
+          <t>Предусловие 2</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>У клиента подключено ДБО</t>
+          <t>Клиент от 18 лет с вкладом «Надёжный» в статусе «Открыт» и открытым текущим счётом в рублях. Вклад открыт 30 дней назад на срок 181 день</t>
+        </is>
+      </c>
+      <c r="J112" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт 4518 990112; вклад 42305810100000034561, сумма 100 000,00 ₽; счёт 40817810300000034562, остаток 5 000,00 ₽</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G113" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K113" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>Предусловие 3</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>У клиента подключено ДБО</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="E114" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Параметры закрытия»</t>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="E115" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>Проверить сообщения и поля на странице</t>
+          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
         <is>
-          <t>Отображается сообщение о досрочном закрытии и сумма к выплате</t>
+          <t>Открылась страница «Параметры закрытия»</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="E116" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>Открыть список «Счёт для перечисления»</t>
+          <t>Проверить сообщения и поля на странице</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
         <is>
-          <t>В списке отображаются все счета клиента, включая карточные и валютные</t>
+          <t>Отображается сообщение о досрочном закрытии и сумма к выплате</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="E117" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>Выбрать счёт из предусловия и нажать «Далее»</t>
+          <t>Открыть список «Счёт для перечисления»</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Подписание», выбран способ подписания «Электронное»</t>
+          <t>В списке отображаются все счета клиента, включая карточные и валютные</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Отправить код» и подождать СМС примерно минуту</t>
+          <t>Выбрать счёт из предусловия и нажать «Далее»</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
         <is>
-          <t>Клиенту отправлено СМС с кодом</t>
+          <t>Открылась страница «Подписание», выбран способ подписания «Электронное»</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>Ввести код в поле «Код из СМС» и нажать «Подписать»</t>
+          <t>Нажать «Отправить код» и подождать СМС примерно минуту</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Заявка направлена на подтверждение контролёру», заявка в статусе «На подтверждении»</t>
-        </is>
-      </c>
-      <c r="J119" s="2" t="inlineStr">
-        <is>
-          <t>Код из СМС, пришедшего на тестовый номер клиента</t>
+          <t>Клиенту отправлено СМС с кодом</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Шаг 8</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
+          <t>Ввести код в поле «Код из СМС» и нажать «Подписать»</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница входа в ЕФР</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900906 «Выход из ЕФР»</t>
+          <t>Выводится сообщение «Заявка направлена на подтверждение контролёру», заявка в статусе «На подтверждении»</t>
+        </is>
+      </c>
+      <c r="J120" s="2" t="inlineStr">
+        <is>
+          <t>Код из СМС, пришедшего на тестовый номер клиента</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="E121" s="2" t="inlineStr">
         <is>
-          <t>Шаг 9</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
-        </is>
-      </c>
-      <c r="J121" s="2" t="inlineStr">
-        <is>
-          <t>tst_contr01</t>
+          <t>Открылась страница входа в ЕФР</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
+          <t>Общий шаг 900906 «Выход из ЕФР»</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="E122" s="2" t="inlineStr">
         <is>
-          <t>Шаг 10</t>
+          <t>Шаг 9</t>
         </is>
       </c>
       <c r="G122" s="2" t="inlineStr">
         <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
+          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
+        </is>
+      </c>
+      <c r="J122" s="2" t="inlineStr">
+        <is>
+          <t>tst_contr01</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="E123" s="2" t="inlineStr">
         <is>
-          <t>Шаг 11</t>
+          <t>Шаг 10</t>
         </is>
       </c>
       <c r="G123" s="2" t="inlineStr">
         <is>
-          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>Открылась форма заявки в статусе «На подтверждении»</t>
+          <t>Нажать ссылку «Задачи» в хедере</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -3121,310 +3116,310 @@
     <row r="124">
       <c r="E124" s="2" t="inlineStr">
         <is>
+          <t>Шаг 11</t>
+        </is>
+      </c>
+      <c r="G124" s="2" t="inlineStr">
+        <is>
+          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>Открылась форма заявки в статусе «На подтверждении»</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="E125" s="2" t="inlineStr">
+        <is>
           <t>Шаг 12</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr">
         <is>
           <t>Нажать «Подтвердить»</t>
         </is>
       </c>
-      <c r="I124" s="2" t="inlineStr">
+      <c r="I125" s="2" t="inlineStr">
         <is>
           <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт»</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>900411</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Несовершеннолетний клиент</t>
         </is>
       </c>
-      <c r="C125" s="2" t="inlineStr">
+      <c r="C126" s="2" t="inlineStr">
         <is>
           <t>Закрытие вклада несовершеннолетнему клиенту с участием законного представителя</t>
         </is>
       </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M125" s="2" t="inlineStr">
+      <c r="M126" s="2" t="inlineStr">
         <is>
           <t>Высокий</t>
         </is>
       </c>
-      <c r="N125" s="2" t="inlineStr">
+      <c r="N126" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O125" s="2" t="inlineStr">
+      <c r="O126" s="2" t="inlineStr">
         <is>
           <t>9/22/2026 14:17:36</t>
         </is>
       </c>
-      <c r="P125" s="2" t="inlineStr">
+      <c r="P126" s="2" t="inlineStr">
         <is>
           <t>Ксения Литвинова</t>
         </is>
       </c>
-      <c r="Q125" s="2" t="inlineStr">
+      <c r="Q126" s="2" t="inlineStr">
         <is>
           <t>biq90102, deposit, minor</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="E126" s="2" t="inlineStr">
-        <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F126" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
-        </is>
-      </c>
-      <c r="I126" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J126" s="2" t="inlineStr">
-        <is>
-          <t>tst_oper01</t>
-        </is>
-      </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="E127" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
+          <t>Предусловие 1</t>
         </is>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
-          <t>Клиенту 16 лет. У клиента вклад «До востребования» в статусе «Открыт» и текущий счёт в рублях, ДБО подключено с полным доступом</t>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
+        </is>
+      </c>
+      <c r="I127" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
         </is>
       </c>
       <c r="J127" s="2" t="inlineStr">
         <is>
-          <t>Паспорт 4519 001223; вклад 42301810500000045671; счёт 40817810700000045672</t>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="E128" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 3</t>
+          <t>Предусловие 2</t>
         </is>
       </c>
       <c r="F128" s="2" t="inlineStr">
         <is>
-          <t>Законный представитель клиента — клиент Банка</t>
+          <t>Клиенту 16 лет. У клиента вклад «До востребования» в статусе «Открыт» и текущий счёт в рублях, ДБО подключено с полным доступом</t>
+        </is>
+      </c>
+      <c r="J128" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт 4519 001223; вклад 42301810500000045671; счёт 40817810700000045672</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="E129" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
-        </is>
-      </c>
-      <c r="I129" s="2" t="inlineStr">
-        <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>Предусловие 3</t>
+        </is>
+      </c>
+      <c r="F129" s="2" t="inlineStr">
+        <is>
+          <t>Законный представитель клиента — клиент Банка</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="E130" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G130" s="2" t="inlineStr">
         <is>
-          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
         </is>
       </c>
       <c r="I130" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Параметры закрытия». Выводится сообщение «Клиент несовершеннолетний. Для закрытия вклада нужен законный представитель.», отображается блок «Законный представитель», кнопка «Далее» неактивна</t>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="E131" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G131" s="2" t="inlineStr">
         <is>
-          <t>В блоке «Законный представитель» найти представителя по паспорту и выбрать его</t>
+          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
         </is>
       </c>
       <c r="I131" s="2" t="inlineStr">
         <is>
-          <t>В блоке отображаются ФИО и паспорт представителя</t>
+          <t>Открылась страница «Параметры закрытия». Выводится сообщение «Клиент несовершеннолетний. Для закрытия вклада нужен законный представитель.», отображается блок «Законный представитель», кнопка «Далее» неактивна</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="E132" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G132" s="2" t="inlineStr">
         <is>
-          <t>В поле «Счёт для перечисления» выбрать счёт из предусловия</t>
+          <t>В блоке «Законный представитель» найти представителя по паспорту и выбрать его</t>
         </is>
       </c>
       <c r="I132" s="2" t="inlineStr">
         <is>
-          <t>Счёт выбран</t>
+          <t>В блоке отображаются ФИО и паспорт представителя</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="E133" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G133" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Далее»</t>
+          <t>В поле «Счёт для перечисления» выбрать счёт из предусловия</t>
         </is>
       </c>
       <c r="I133" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Подписание», выбран способ подписания «Электронное», его можно сменить на «Бумажное»</t>
+          <t>Счёт выбран</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="E134" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G134" s="2" t="inlineStr">
         <is>
-          <t>Выбрать способ «Бумажное», в поле «Уполномоченное лицо банка» выбрать текущего пользователя, нажать «Печать», затем «Документы подписаны»</t>
+          <t>Нажать «Далее»</t>
         </is>
       </c>
       <c r="I134" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Заявка направлена на подтверждение контролёру», заявка в статусе «На подтверждении»</t>
+          <t>Открылась страница «Подписание», выбран способ подписания «Электронное», его можно сменить на «Бумажное»</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="E135" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G135" s="2" t="inlineStr">
         <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
+          <t>Выбрать способ «Бумажное», в поле «Уполномоченное лицо банка» выбрать текущего пользователя, нажать «Печать», затем «Документы подписаны»</t>
         </is>
       </c>
       <c r="I135" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница входа в ЕФР</t>
-        </is>
-      </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900906 «Выход из ЕФР»</t>
+          <t>Выводится сообщение «Заявка направлена на подтверждение контролёру», заявка в статусе «На подтверждении»</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="E136" s="2" t="inlineStr">
         <is>
-          <t>Шаг 8</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G136" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
         </is>
       </c>
       <c r="I136" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
-        </is>
-      </c>
-      <c r="J136" s="2" t="inlineStr">
-        <is>
-          <t>tst_contr01</t>
+          <t>Открылась страница входа в ЕФР</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
+          <t>Общий шаг 900906 «Выход из ЕФР»</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="E137" s="2" t="inlineStr">
         <is>
-          <t>Шаг 9</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G137" s="2" t="inlineStr">
         <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
+          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+        </is>
+      </c>
+      <c r="I137" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
+        </is>
+      </c>
+      <c r="J137" s="2" t="inlineStr">
+        <is>
+          <t>tst_contr01</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="E138" s="2" t="inlineStr">
         <is>
-          <t>Шаг 10</t>
+          <t>Шаг 9</t>
         </is>
       </c>
       <c r="G138" s="2" t="inlineStr">
         <is>
-          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
-        </is>
-      </c>
-      <c r="I138" s="2" t="inlineStr">
-        <is>
-          <t>Открылась форма заявки в статусе «На подтверждении»</t>
+          <t>Нажать ссылку «Задачи» в хедере</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -3436,525 +3431,525 @@
     <row r="139">
       <c r="E139" s="2" t="inlineStr">
         <is>
+          <t>Шаг 10</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
+        </is>
+      </c>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>Открылась форма заявки в статусе «На подтверждении»</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="E140" s="2" t="inlineStr">
+        <is>
           <t>Шаг 11</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr">
         <is>
           <t>Нажать «Подтвердить»</t>
         </is>
       </c>
-      <c r="I139" s="2" t="inlineStr">
+      <c r="I140" s="2" t="inlineStr">
         <is>
           <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт», остаток вклада выдан законному представителю наличными через кассу</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>900412</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Несовершеннолетний клиент</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>Закрытие вклада совершеннолетнему клиенту</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>Закрытие вклада несовершеннолетнему клиенту</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M140" s="2" t="inlineStr">
+      <c r="M141" s="2" t="inlineStr">
         <is>
           <t>Высокий</t>
         </is>
       </c>
-      <c r="N140" s="2" t="inlineStr">
+      <c r="N141" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O140" s="2" t="inlineStr">
+      <c r="O141" s="2" t="inlineStr">
         <is>
           <t>9/23/2026 10:44:03</t>
         </is>
       </c>
-      <c r="P140" s="2" t="inlineStr">
+      <c r="P141" s="2" t="inlineStr">
         <is>
           <t>Ирина Соловьёва</t>
         </is>
       </c>
-      <c r="Q140" s="2" t="inlineStr">
+      <c r="Q141" s="2" t="inlineStr">
         <is>
           <t>biq90102, deposit, dbo</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
-        </is>
-      </c>
-      <c r="I141" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J141" s="2" t="inlineStr">
-        <is>
-          <t>tst_kmtp01</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="E142" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
+          <t>Предусловие 1</t>
         </is>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
-          <t>Клиенту сегодня исполняется 18 лет. У клиента вклад «До востребования» в статусе «Открыт» и текущий счёт в рублях, ДБО подключено с полным доступом</t>
+          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
+        </is>
+      </c>
+      <c r="I142" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
         </is>
       </c>
       <c r="J142" s="2" t="inlineStr">
         <is>
-          <t>Паспорт 4520 112334; дата рождения — сегодняшняя дата 18 лет назад; вклад 42301810800000056781; счёт 40817810100000056782</t>
+          <t>tst_kmtp01</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="E143" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G143" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
-        </is>
-      </c>
-      <c r="I143" s="2" t="inlineStr">
-        <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F143" s="2" t="inlineStr">
+        <is>
+          <t>Клиенту сегодня исполняется 18 лет. У клиента вклад «До востребования» в статусе «Открыт» и текущий счёт в рублях, ДБО подключено с полным доступом</t>
+        </is>
+      </c>
+      <c r="J143" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт 4520 112334; дата рождения — сегодняшняя дата 18 лет назад; вклад 42301810800000056781; счёт 40817810100000056782</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="E144" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G144" s="2" t="inlineStr">
         <is>
-          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
         </is>
       </c>
       <c r="I144" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Параметры закрытия», блок «Законный представитель» не отображается</t>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="E145" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G145" s="2" t="inlineStr">
         <is>
-          <t>Проверить сообщения на странице</t>
+          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Вклад закрывается досрочно. Проценты будут пересчитаны по ставке 0,01% годовых.»</t>
+          <t>Открылась страница «Параметры закрытия», блок «Законный представитель» не отображается</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="E146" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G146" s="2" t="inlineStr">
         <is>
-          <t>В поле «Счёт для перечисления» выбрать счёт из предусловия и нажать «Далее»</t>
+          <t>Проверить сообщения на странице</t>
         </is>
       </c>
       <c r="I146" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Подписание», выбран способ подписания «Электронное»</t>
+          <t>Выводится сообщение «Вклад закрывается досрочно. Проценты будут пересчитаны по ставке 0,01% годовых.»</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="E147" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G147" s="2" t="inlineStr">
         <is>
-          <t>Клиент получил СМС с кодом</t>
+          <t>В поле «Счёт для перечисления» выбрать счёт из предусловия и нажать «Далее»</t>
+        </is>
+      </c>
+      <c r="I147" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Подписание», выбран способ подписания «Электронное»</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="E148" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G148" s="2" t="inlineStr">
         <is>
-          <t>Ввести в поле «Код из СМС» неверный код и нажать «Подписать»</t>
-        </is>
-      </c>
-      <c r="I148" s="2" t="inlineStr">
-        <is>
-          <t>Выводится сообщение «Неверный код. Осталось попыток: 2»</t>
-        </is>
-      </c>
-      <c r="J148" s="2" t="inlineStr">
-        <is>
-          <t>000000</t>
+          <t>Клиент получил СМС с кодом</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="E149" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G149" s="2" t="inlineStr">
         <is>
-          <t>Ввести верный код из СМС и нажать «Подписать»</t>
+          <t>Ввести в поле «Код из СМС» неверный код и нажать «Подписать»</t>
         </is>
       </c>
       <c r="I149" s="2" t="inlineStr">
         <is>
-          <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт», подтверждение контролёром не требуется</t>
+          <t>Выводится сообщение «Неверный код. Осталось попыток: 2»</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="inlineStr">
+        <is>
+          <t>000000</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="E150" s="2" t="inlineStr">
         <is>
+          <t>Шаг 7</t>
+        </is>
+      </c>
+      <c r="G150" s="2" t="inlineStr">
+        <is>
+          <t>Ввести верный код из СМС и нажать «Подписать»</t>
+        </is>
+      </c>
+      <c r="I150" s="2" t="inlineStr">
+        <is>
+          <t>Заявка в статусе «Исполнена», вклад в статусе «Закрыт», подтверждение контролёром не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="E151" s="2" t="inlineStr">
+        <is>
           <t>Шаг 8</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr">
         <is>
           <t>Открыть счёт для перечисления</t>
         </is>
       </c>
-      <c r="I150" s="2" t="inlineStr">
+      <c r="I151" s="2" t="inlineStr">
         <is>
           <t>Сумма вклада зачислена на счёт</t>
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>900413</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие вклада</t>
         </is>
       </c>
-      <c r="C151" s="2" t="inlineStr">
+      <c r="C152" s="2" t="inlineStr">
         <is>
           <t>Закрытие вклада без полного доступа в ДБО: бумажное подписание и подтверждение контролёром</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M151" s="2" t="inlineStr">
+      <c r="M152" s="2" t="inlineStr">
         <is>
           <t>Самый высокий</t>
         </is>
       </c>
-      <c r="N151" s="2" t="inlineStr">
+      <c r="N152" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O151" s="2" t="inlineStr">
+      <c r="O152" s="2" t="inlineStr">
         <is>
           <t>9/23/2026 16:02:48</t>
         </is>
       </c>
-      <c r="P151" s="2" t="inlineStr">
+      <c r="P152" s="2" t="inlineStr">
         <is>
           <t>Павел Ермаков</t>
         </is>
       </c>
-      <c r="Q151" s="2" t="inlineStr">
+      <c r="Q152" s="2" t="inlineStr">
         <is>
           <t>biq90102, deposit, control</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="E152" s="2" t="inlineStr">
-        <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F152" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
-        </is>
-      </c>
-      <c r="I152" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J152" s="2" t="inlineStr">
-        <is>
-          <t>tst_oper01</t>
-        </is>
-      </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="E153" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
+          <t>Предусловие 1</t>
         </is>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
-          <t>Клиент от 18 лет с вкладом «Пополняемый» в статусе «Открыт», срок вклада не закончился, и текущим счётом в рублях. ДБО подключено, уровень доступа «Ограниченный»</t>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
+        </is>
+      </c>
+      <c r="I153" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
         </is>
       </c>
       <c r="J153" s="2" t="inlineStr">
         <is>
-          <t>Паспорт 4521 223445; вклад 42305810400000067891, сумма 50 000,00 ₽, открыт 73 дня назад на срок 181 день; счёт 40817810400000067892</t>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="E154" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G154" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
-        </is>
-      </c>
-      <c r="I154" s="2" t="inlineStr">
-        <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F154" s="2" t="inlineStr">
+        <is>
+          <t>Клиент от 18 лет с вкладом «Пополняемый» в статусе «Открыт», срок вклада не закончился, и текущим счётом в рублях. ДБО подключено, уровень доступа «Ограниченный»</t>
+        </is>
+      </c>
+      <c r="J154" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт 4521 223445; вклад 42305810400000067891, сумма 50 000,00 ₽, открыт 73 дня назад на срок 181 день; счёт 40817810400000067892</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="E155" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G155" s="2" t="inlineStr">
         <is>
-          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
         </is>
       </c>
       <c r="I155" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «У Клиента отсутствует «полный доступ» в ДБО. Электронное подписание недоступно» с кнопками «Продолжить с бумажным подписанием» и «Отмена»</t>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="E156" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G156" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Продолжить с бумажным подписанием»</t>
+          <t>Напротив вклада нажать «Показать», затем «Операции» и выбрать «Закрыть вклад»</t>
         </is>
       </c>
       <c r="I156" s="2" t="inlineStr">
         <is>
-          <t>Открылась форма «Закрытие вклада»</t>
+          <t>Выводится сообщение «У Клиента отсутствует «полный доступ» в ДБО. Электронное подписание недоступно» с кнопками «Продолжить с бумажным подписанием» и «Отмена»</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="E157" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G157" s="2" t="inlineStr">
         <is>
-          <t>В поле «Счёт для перечисления» выбрать счёт из предусловия</t>
+          <t>Нажать «Продолжить с бумажным подписанием»</t>
         </is>
       </c>
       <c r="I157" s="2" t="inlineStr">
         <is>
-          <t>В поле «Счёт для перечисления» — 40817810400000067892</t>
+          <t>Открылась форма «Закрытие вклада»</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="E158" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G158" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Далее»</t>
+          <t>В поле «Счёт для перечисления» выбрать счёт из предусловия</t>
         </is>
       </c>
       <c r="I158" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница «Подписание», способ подписания «Бумажное»</t>
+          <t>В поле «Счёт для перечисления» — 40817810400000067892</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="E159" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G159" s="2" t="inlineStr">
         <is>
-          <t>В поле «Уполномоченное лицо банка» выбрать текущего пользователя, нажать «Документы подписаны», затем «Печать»</t>
+          <t>Нажать «Далее»</t>
         </is>
       </c>
       <c r="I159" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Заявка направлена на подтверждение контролёру», заявка в статусе «На подтверждении»</t>
+          <t>Открылась страница «Подписание», способ подписания «Бумажное»</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="E160" s="2" t="inlineStr">
         <is>
-          <t>Постусловие 1</t>
-        </is>
-      </c>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
+          <t>Шаг 6</t>
+        </is>
+      </c>
+      <c r="G160" s="2" t="inlineStr">
+        <is>
+          <t>В поле «Уполномоченное лицо банка» выбрать текущего пользователя, нажать «Документы подписаны», затем «Печать»</t>
         </is>
       </c>
       <c r="I160" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница входа в ЕФР</t>
-        </is>
-      </c>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900906 «Выход из ЕФР»</t>
+          <t>Выводится сообщение «Заявка направлена на подтверждение контролёру», заявка в статусе «На подтверждении»</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="E161" s="2" t="inlineStr">
         <is>
-          <t>Постусловие 2</t>
+          <t>Постусловие 1</t>
         </is>
       </c>
       <c r="H161" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
         </is>
       </c>
       <c r="I161" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
-        </is>
-      </c>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t>tst_contr01</t>
+          <t>Открылась страница входа в ЕФР</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
+          <t>Общий шаг 900906 «Выход из ЕФР»</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="E162" s="2" t="inlineStr">
         <is>
-          <t>Постусловие 3</t>
+          <t>Постусловие 2</t>
         </is>
       </c>
       <c r="H162" s="2" t="inlineStr">
         <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
+          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+        </is>
+      </c>
+      <c r="I162" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
+        </is>
+      </c>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>tst_contr01</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="E163" s="2" t="inlineStr">
         <is>
-          <t>Постусловие 4</t>
+          <t>Постусловие 3</t>
         </is>
       </c>
       <c r="H163" s="2" t="inlineStr">
         <is>
-          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
-        </is>
-      </c>
-      <c r="I163" s="2" t="inlineStr">
-        <is>
-          <t>Открылась форма заявки в статусе «На подтверждении»</t>
+          <t>Нажать ссылку «Задачи» в хедере</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -3966,276 +3961,276 @@
     <row r="164">
       <c r="E164" s="2" t="inlineStr">
         <is>
+          <t>Постусловие 4</t>
+        </is>
+      </c>
+      <c r="H164" s="2" t="inlineStr">
+        <is>
+          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
+        </is>
+      </c>
+      <c r="I164" s="2" t="inlineStr">
+        <is>
+          <t>Открылась форма заявки в статусе «На подтверждении»</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="E165" s="2" t="inlineStr">
+        <is>
           <t>Постусловие 5</t>
         </is>
       </c>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>Нажать «Подтвердить»</t>
         </is>
       </c>
-      <c r="I164" s="2" t="inlineStr">
+      <c r="I165" s="2" t="inlineStr">
         <is>
           <t>Заявка подтверждена</t>
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>900414</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 5. Счета и вклады ФЛ -&gt; 5.3 BIQ-90102 Закрытие счёта и вклада -&gt; Закрытие счёта</t>
         </is>
       </c>
-      <c r="C165" s="2" t="inlineStr">
+      <c r="C166" s="2" t="inlineStr">
         <is>
           <t>Закрытие текущего счёта с нулевым остатком, электронное подписание</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M165" s="2" t="inlineStr">
+      <c r="M166" s="2" t="inlineStr">
         <is>
           <t>Высокий</t>
         </is>
       </c>
-      <c r="N165" s="2" t="inlineStr">
+      <c r="N166" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O165" s="2" t="inlineStr">
+      <c r="O166" s="2" t="inlineStr">
         <is>
           <t>9/24/2026 11:20:15</t>
         </is>
       </c>
-      <c r="P165" s="2" t="inlineStr">
+      <c r="P166" s="2" t="inlineStr">
         <is>
           <t>Павел Ермаков</t>
         </is>
       </c>
-      <c r="Q165" s="2" t="inlineStr">
+      <c r="Q166" s="2" t="inlineStr">
         <is>
           <t>biq90102, account, dbo</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="E166" s="2" t="inlineStr">
-        <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F166" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли финансового консультанта ТП</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J166" s="2" t="inlineStr">
-        <is>
-          <t>tst_fk01</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="E167" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
+          <t>Предусловие 1</t>
         </is>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
-          <t>У клиента любой текущий или карточный счёт в рублях с остатком 0,00 ₽, ДБО подключено с полным доступом</t>
+          <t>Выполнить вход в ЕФР в роли финансового консультанта ТП</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
         </is>
       </c>
       <c r="J167" s="2" t="inlineStr">
         <is>
-          <t>Паспорт 4522 334556</t>
+          <t>tst_fk01</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="E168" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G168" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
-        </is>
-      </c>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F168" s="2" t="inlineStr">
+        <is>
+          <t>У клиента любой текущий или карточный счёт в рублях с остатком 0,00 ₽, ДБО подключено с полным доступом</t>
+        </is>
+      </c>
+      <c r="J168" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт 4522 334556</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="E169" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G169" s="2" t="inlineStr">
         <is>
-          <t>Напротив счёта нажать «Показать», затем «Операции» и выбрать «Закрыть счёт»</t>
+          <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
         </is>
       </c>
       <c r="I169" s="2" t="inlineStr">
         <is>
-          <t>Открылась форма «Закрытие счёта», остаток 0,00 ₽, выбран способ подписания «Электронное»</t>
+          <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900905 «Поиск клиента по паспорту»</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="E170" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G170" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Отправить код»</t>
+          <t>Напротив счёта нажать «Показать», затем «Операции» и выбрать «Закрыть счёт»</t>
         </is>
       </c>
       <c r="I170" s="2" t="inlineStr">
         <is>
-          <t>Клиенту отправлено СМС, доступно поле «Код из СМС»</t>
+          <t>Открылась форма «Закрытие счёта», остаток 0,00 ₽, выбран способ подписания «Электронное»</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="E171" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G171" s="2" t="inlineStr">
         <is>
-          <t>Ввести в поле «Код из СМС» код, полученный на шаге 9</t>
+          <t>Нажать «Отправить код»</t>
         </is>
       </c>
       <c r="I171" s="2" t="inlineStr">
         <is>
-          <t>В поле «Код из СМС» — 6 цифр</t>
+          <t>Клиенту отправлено СМС, доступно поле «Код из СМС»</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="E172" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G172" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Подписать»</t>
+          <t>Ввести в поле «Код из СМС» код, полученный на шаге 9</t>
         </is>
       </c>
       <c r="I172" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Заявка направлена на подтверждение контролёру», заявка в статусе «На подтверждении»</t>
+          <t>В поле «Код из СМС» — 6 цифр</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="E173" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G173" s="2" t="inlineStr">
         <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
+          <t>Нажать «Подписать»</t>
         </is>
       </c>
       <c r="I173" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница входа в ЕФР</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900906 «Выход из ЕФР»</t>
+          <t>Выводится сообщение «Заявка направлена на подтверждение контролёру», заявка в статусе «На подтверждении»</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="E174" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G174" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
         </is>
       </c>
       <c r="I174" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
-        </is>
-      </c>
-      <c r="J174" s="2" t="inlineStr">
-        <is>
-          <t>tst_contr01</t>
+          <t>Открылась страница входа в ЕФР</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
+          <t>Общий шаг 900906 «Выход из ЕФР»</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="E175" s="2" t="inlineStr">
         <is>
-          <t>Шаг 8</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G175" s="2" t="inlineStr">
         <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
+          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>tst_contr01</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="E176" s="2" t="inlineStr">
         <is>
-          <t>Шаг 9</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G176" s="2" t="inlineStr">
         <is>
-          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
-        </is>
-      </c>
-      <c r="I176" s="2" t="inlineStr">
-        <is>
-          <t>Открылась форма заявки в статусе «На подтверждении»</t>
+          <t>Нажать ссылку «Задачи» в хедере</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
@@ -4247,281 +4242,281 @@
     <row r="177">
       <c r="E177" s="2" t="inlineStr">
         <is>
+          <t>Шаг 9</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>Открылась форма заявки в статусе «На подтверждении»</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="E178" s="2" t="inlineStr">
+        <is>
           <t>Шаг 10</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr">
         <is>
           <t>Нажать «Подтвердить»</t>
         </is>
       </c>
-      <c r="I177" s="2" t="inlineStr">
+      <c r="I178" s="2" t="inlineStr">
         <is>
           <t>Счёт закрыт корректно</t>
         </is>
       </c>
     </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>900415</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Проверка на дубль</t>
         </is>
       </c>
-      <c r="C178" s="2" t="inlineStr">
+      <c r="C179" s="2" t="inlineStr">
         <is>
           <t>Создание клиента: совпали ФИО и дата рождения, нет предыдущего паспорта — подтверждение контролёром</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M178" s="2" t="inlineStr">
+      <c r="M179" s="2" t="inlineStr">
         <is>
           <t>Самый высокий</t>
         </is>
       </c>
-      <c r="N178" s="2" t="inlineStr">
+      <c r="N179" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O178" s="2" t="inlineStr">
+      <c r="O179" s="2" t="inlineStr">
         <is>
           <t>9/28/2026 10:09:27</t>
         </is>
       </c>
-      <c r="P178" s="2" t="inlineStr">
+      <c r="P179" s="2" t="inlineStr">
         <is>
           <t>Дарья Мельникова</t>
         </is>
       </c>
-      <c r="Q178" s="2" t="inlineStr">
+      <c r="Q179" s="2" t="inlineStr">
         <is>
           <t>biq90103, client, duplicate, control</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="E179" s="2" t="inlineStr">
-        <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F179" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
-        </is>
-      </c>
-      <c r="I179" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J179" s="2" t="inlineStr">
-        <is>
-          <t>tst_kmtp01</t>
-        </is>
-      </c>
-      <c r="K179" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900903 «Вход в ЕФР в роли клиентского менеджера»</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="E180" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
+          <t>Предусловие 1</t>
         </is>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
-          <t>В ЕФР есть клиент Семёнова Алёна с датой рождения 12.03.1990</t>
+          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
         </is>
       </c>
       <c r="J180" s="2" t="inlineStr">
         <is>
-          <t>Паспорт существующего клиента 4512 300111</t>
+          <t>tst_kmtp01</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900903 «Вход в ЕФР в роли клиентского менеджера»</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="E181" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G181" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
-        </is>
-      </c>
-      <c r="I181" s="2" t="inlineStr">
-        <is>
-          <t>Открылась анкета «Создание клиента»</t>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>В ЕФР есть клиент Семёнова Алёна, отчество отсутствует, дата рождения 12.03.1990</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>Паспорт существующего клиента 4512 300111</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="E182" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G182" s="2" t="inlineStr">
         <is>
-          <t>Ввести ФИО и дату рождения нового клиента</t>
+          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
         </is>
       </c>
       <c r="I182" s="2" t="inlineStr">
         <is>
-          <t>В полях отображаются введённые значения</t>
-        </is>
-      </c>
-      <c r="J182" s="2" t="inlineStr">
-        <is>
-          <t>Фамилия СЕМЕНОВА, имя АЛЕНА, отчество ИГОРЕВНА, дата рождения 12.03.1990</t>
+          <t>Открылась анкета «Создание клиента»</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="E183" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G183" s="2" t="inlineStr">
         <is>
-          <t>Заполнить остальные обязательные поля анкеты</t>
+          <t>Ввести ФИО и дату рождения нового клиента</t>
         </is>
       </c>
       <c r="I183" s="2" t="inlineStr">
         <is>
-          <t>Все обязательные поля анкеты заполнены</t>
+          <t>В полях отображаются введённые значения</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>Фамилия СЕМЕНОВА, имя АЛЕНА, отчество ИГОРЕВНА, дата рождения 12.03.1990</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="E184" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G184" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Сохранить»</t>
+          <t>Заполнить остальные обязательные поля анкеты</t>
         </is>
       </c>
       <c r="I184" s="2" t="inlineStr">
         <is>
-          <t>Открылось окно «Обратите внимание» с текстом «Клиент с такими ФИО и датой рождения уже есть в системе. Укажите данные предыдущего паспорта РФ, чтобы не создать дубль карточки.» и кнопками «Ввести данные предыдущего паспорта» и «Нет предыдущего ДУЛ»</t>
+          <t>Все обязательные поля анкеты заполнены</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="E185" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G185" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Нет предыдущего ДУЛ»</t>
+          <t>Нажать «Сохранить»</t>
         </is>
       </c>
       <c r="I185" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Операция требует подтверждения контролирующим работником», заявка в статусе «На подтверждении»</t>
+          <t>Открылось окно «Обратите внимание» с текстом «Клиент с такими ФИО и датой рождения уже есть в системе. Укажите данные предыдущего паспорта РФ, чтобы не создать дубль карточки.» и кнопками «Ввести данные предыдущего паспорта» и «Нет предыдущего ДУЛ»</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="E186" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G186" s="2" t="inlineStr">
         <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
+          <t>Нажать «Нет предыдущего ДУЛ»</t>
         </is>
       </c>
       <c r="I186" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница входа в ЕФР</t>
-        </is>
-      </c>
-      <c r="K186" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900906 «Выход из ЕФР»</t>
+          <t>Выводится сообщение «Операция требует подтверждения контролирующим работником», заявка в статусе «На подтверждении»</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="E187" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G187" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
         </is>
       </c>
       <c r="I187" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
-        </is>
-      </c>
-      <c r="J187" s="2" t="inlineStr">
-        <is>
-          <t>tst_contr01</t>
+          <t>Открылась страница входа в ЕФР</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
+          <t>Общий шаг 900906 «Выход из ЕФР»</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="E188" s="2" t="inlineStr">
         <is>
-          <t>Шаг 8</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G188" s="2" t="inlineStr">
         <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
+          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+        </is>
+      </c>
+      <c r="I188" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
+        </is>
+      </c>
+      <c r="J188" s="2" t="inlineStr">
+        <is>
+          <t>tst_contr01</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="E189" s="2" t="inlineStr">
         <is>
-          <t>Шаг 9</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G189" s="2" t="inlineStr">
         <is>
-          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
-        </is>
-      </c>
-      <c r="I189" s="2" t="inlineStr">
-        <is>
-          <t>Открылась форма заявки в статусе «На подтверждении»</t>
+          <t>Нажать ссылку «Задачи» в хедере</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -4533,1104 +4528,1104 @@
     <row r="190">
       <c r="E190" s="2" t="inlineStr">
         <is>
-          <t>Шаг 10</t>
+          <t>Шаг 9</t>
         </is>
       </c>
       <c r="G190" s="2" t="inlineStr">
         <is>
-          <t>Проверить блок «Внимание» на форме заявки</t>
+          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
         </is>
       </c>
       <c r="I190" s="2" t="inlineStr">
         <is>
-          <t>Отображается уведомление о возможном дубле клиента</t>
+          <t>Открылась форма заявки в статусе «На подтверждении»</t>
+        </is>
+      </c>
+      <c r="K190" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="E191" s="2" t="inlineStr">
         <is>
+          <t>Шаг 10</t>
+        </is>
+      </c>
+      <c r="G191" s="2" t="inlineStr">
+        <is>
+          <t>Проверить блок «Внимание» на форме заявки</t>
+        </is>
+      </c>
+      <c r="I191" s="2" t="inlineStr">
+        <is>
+          <t>Отображается уведомление о возможном дубле клиента</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="E192" s="2" t="inlineStr">
+        <is>
           <t>Шаг 11</t>
         </is>
       </c>
-      <c r="G191" s="2" t="inlineStr">
+      <c r="G192" s="2" t="inlineStr">
         <is>
           <t>Нажать «Подтвердить операцию»</t>
         </is>
       </c>
-      <c r="I191" s="2" t="inlineStr">
+      <c r="I192" s="2" t="inlineStr">
         <is>
           <t>Выводится сообщение «Карточка клиента сохранена», клиент в статусе «Черновик»</t>
         </is>
       </c>
     </row>
-    <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+    <row r="193">
+      <c r="A193" s="2" t="inlineStr">
         <is>
           <t>900416</t>
         </is>
       </c>
-      <c r="B192" s="2" t="inlineStr">
+      <c r="B193" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Проверка на дубль</t>
         </is>
       </c>
-      <c r="C192" s="2" t="inlineStr">
+      <c r="C193" s="2" t="inlineStr">
         <is>
           <t>Создание клиента: предыдущий паспорт принадлежит найденному клиенту — новая карточка не создаётся</t>
         </is>
       </c>
-      <c r="D192" s="2" t="inlineStr">
+      <c r="D193" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M192" s="2" t="inlineStr">
+      <c r="M193" s="2" t="inlineStr">
         <is>
           <t>Высокий</t>
         </is>
       </c>
-      <c r="N192" s="2" t="inlineStr">
+      <c r="N193" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O192" s="2" t="inlineStr">
+      <c r="O193" s="2" t="inlineStr">
         <is>
           <t>9/28/2026 14:51:06</t>
         </is>
       </c>
-      <c r="P192" s="2" t="inlineStr">
+      <c r="P193" s="2" t="inlineStr">
         <is>
           <t>Дарья Мельникова</t>
         </is>
       </c>
-      <c r="Q192" s="2" t="inlineStr">
+      <c r="Q193" s="2" t="inlineStr">
         <is>
           <t>biq90103, client, duplicate</t>
-        </is>
-      </c>
-    </row>
-    <row r="193">
-      <c r="E193" s="2" t="inlineStr">
-        <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F193" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
-        </is>
-      </c>
-      <c r="I193" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J193" s="2" t="inlineStr">
-        <is>
-          <t>tst_oper01</t>
-        </is>
-      </c>
-      <c r="K193" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="E194" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
+          <t>Предусловие 1</t>
         </is>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
-          <t>В ЕФР есть клиент Карпов Олег Дмитриевич, дата рождения 05.07.1985, текущий паспорт 4515 404001, прежний паспорт 4505 404000</t>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
+        </is>
+      </c>
+      <c r="I194" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J194" s="2" t="inlineStr">
+        <is>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K194" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="E195" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G195" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
-        </is>
-      </c>
-      <c r="I195" s="2" t="inlineStr">
-        <is>
-          <t>Открылась анкета «Создание клиента»</t>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F195" s="2" t="inlineStr">
+        <is>
+          <t>В ЕФР есть клиент Карпов Олег Дмитриевич, дата рождения 05.07.1985, текущий паспорт 4515 404001, прежний паспорт 4505 404000</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="E196" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G196" s="2" t="inlineStr">
         <is>
-          <t>Заполнить анкету: ФИО и дата рождения — как у клиента из предусловия 2, новый паспорт, остальные поля — из тестовых данных</t>
+          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
         </is>
       </c>
       <c r="I196" s="2" t="inlineStr">
         <is>
-          <t>В анкете заполнены все обязательные поля</t>
-        </is>
-      </c>
-      <c r="J196" s="2" t="inlineStr">
-        <is>
-          <t>Карпов Олег Дмитриевич, 05.07.1985, пол мужской; паспорт 4521 404002, выдан 10.08.2025, код подразделения 500-112, ГУ МВД России по Московской обл.; телефон +7 900 111-22-33; адрес: г. Москва, ул. Тестовая, д. 1, кв. 1</t>
+          <t>Открылась анкета «Создание клиента»</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="E197" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G197" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Сохранить»</t>
+          <t>Заполнить анкету: ФИО и дата рождения — как у клиента из предусловия 2, новый паспорт, остальные поля — из тестовых данных</t>
         </is>
       </c>
       <c r="I197" s="2" t="inlineStr">
         <is>
-          <t>Открылось окно «Обратите внимание» с текстом «Клиент с такими ФИО и датой рождения уже есть в системе. Укажите данные предыдущего паспорта РФ, чтобы не создать дубль карточки.» и кнопками «Ввести данные предыдущего паспорта» и «Нет предыдущего паспорта»</t>
+          <t>В анкете заполнены все обязательные поля</t>
+        </is>
+      </c>
+      <c r="J197" s="2" t="inlineStr">
+        <is>
+          <t>Карпов Олег Дмитриевич, 05.07.1985, пол мужской; паспорт 4521 404002, выдан 10.08.2025, код подразделения 500-112, ГУ МВД России по Московской обл.; телефон +7 900 111-22-33; адрес: г. Москва, ул. Тестовая, д. 1, кв. 1</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="E198" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G198" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Ввести данные предыдущего паспорта»</t>
+          <t>Нажать «Сохранить»</t>
         </is>
       </c>
       <c r="I198" s="2" t="inlineStr">
         <is>
-          <t>Открылись поля «Серия», «Номер», «Дата выдачи» и кнопка «Проверить»</t>
+          <t>Открылось окно «Обратите внимание» с текстом «Клиент с такими ФИО и датой рождения уже есть в системе. Укажите данные предыдущего паспорта РФ, чтобы не создать дубль карточки.» и кнопками «Ввести данные предыдущего паспорта» и «Нет предыдущего паспорта»</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="E199" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G199" s="2" t="inlineStr">
         <is>
-          <t>Ввести серию и номер предыдущего паспорта клиента</t>
+          <t>Нажать «Ввести данные предыдущего паспорта»</t>
         </is>
       </c>
       <c r="I199" s="2" t="inlineStr">
         <is>
-          <t>В полях «Серия» и «Номер» — 4507 и 404999</t>
-        </is>
-      </c>
-      <c r="J199" s="2" t="inlineStr">
-        <is>
-          <t>4507 404999</t>
+          <t>Открылись поля «Серия», «Номер», «Дата выдачи» и кнопка «Проверить»</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="E200" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G200" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Проверить»</t>
+          <t>Ввести серию и номер предыдущего паспорта клиента</t>
         </is>
       </c>
       <c r="I200" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Клиент с таким паспортом уже существует» и кнопка «Открыть карточку»</t>
+          <t>В полях «Серия» и «Номер» — 4507 и 404999</t>
+        </is>
+      </c>
+      <c r="J200" s="2" t="inlineStr">
+        <is>
+          <t>4507 404999</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="E201" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G201" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Открыть карточку»</t>
+          <t>Нажать «Проверить»</t>
         </is>
       </c>
       <c r="I201" s="2" t="inlineStr">
         <is>
-          <t>Открылась карточка клиента</t>
+          <t>Выводится сообщение «Клиент с таким паспортом уже существует» и кнопка «Открыть карточку»</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="E202" s="2" t="inlineStr">
         <is>
+          <t>Шаг 7</t>
+        </is>
+      </c>
+      <c r="G202" s="2" t="inlineStr">
+        <is>
+          <t>Нажать «Открыть карточку»</t>
+        </is>
+      </c>
+      <c r="I202" s="2" t="inlineStr">
+        <is>
+          <t>Открылась карточка клиента</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="E203" s="2" t="inlineStr">
+        <is>
           <t>Шаг 8</t>
         </is>
       </c>
-      <c r="G202" s="2" t="inlineStr">
+      <c r="G203" s="2" t="inlineStr">
         <is>
           <t>Убедиться, что дубль клиента не создан</t>
         </is>
       </c>
-      <c r="I202" s="2" t="inlineStr">
+      <c r="I203" s="2" t="inlineStr">
         <is>
           <t>Дубль не создан</t>
         </is>
       </c>
     </row>
-    <row r="203">
-      <c r="A203" s="2" t="inlineStr">
+    <row r="204">
+      <c r="A204" s="2" t="inlineStr">
         <is>
           <t>900417</t>
         </is>
       </c>
-      <c r="B203" s="2" t="inlineStr">
+      <c r="B204" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Списки финмониторинга</t>
         </is>
       </c>
-      <c r="C203" s="2" t="inlineStr">
+      <c r="C204" s="2" t="inlineStr">
         <is>
           <t>Создание клиента: совпадение со списком финмониторинга, операция продолжается</t>
         </is>
       </c>
-      <c r="D203" s="2" t="inlineStr">
+      <c r="D204" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M203" s="2" t="inlineStr">
+      <c r="M204" s="2" t="inlineStr">
         <is>
           <t>Самый высокий</t>
         </is>
       </c>
-      <c r="N203" s="2" t="inlineStr">
+      <c r="N204" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O203" s="2" t="inlineStr">
+      <c r="O204" s="2" t="inlineStr">
         <is>
           <t>9/29/2026 11:34:40</t>
         </is>
       </c>
-      <c r="P203" s="2" t="inlineStr">
+      <c r="P204" s="2" t="inlineStr">
         <is>
           <t>Владимир Астахов</t>
         </is>
       </c>
-      <c r="Q203" s="2" t="inlineStr">
+      <c r="Q204" s="2" t="inlineStr">
         <is>
           <t>biq90103, client, finmon</t>
-        </is>
-      </c>
-    </row>
-    <row r="204">
-      <c r="E204" s="2" t="inlineStr">
-        <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F204" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
-        </is>
-      </c>
-      <c r="I204" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J204" s="2" t="inlineStr">
-        <is>
-          <t>tst_kmtp01</t>
-        </is>
-      </c>
-      <c r="K204" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900903 «Вход в ЕФР в роли клиентского менеджера»</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="E205" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
+          <t>Предусловие 1</t>
         </is>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
-          <t>Подготовлены данные человека, которого нет в ЕФР и в списках финмониторинга</t>
+          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
+        </is>
+      </c>
+      <c r="I205" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
         </is>
       </c>
       <c r="J205" s="2" t="inlineStr">
         <is>
-          <t>Гусев Роман Ильич, 14.02.1979, пол мужской; паспорт 4518 700701, выдан 03.03.2024, код подразделения 770-045, ГУ МВД России по г. Москве; телефон +7 900 222-33-44; адрес: г. Москва, ул. Тестовая, д. 5, кв. 12</t>
+          <t>tst_kmtp01</t>
+        </is>
+      </c>
+      <c r="K205" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900903 «Вход в ЕФР в роли клиентского менеджера»</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="E206" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G206" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
-        </is>
-      </c>
-      <c r="I206" s="2" t="inlineStr">
-        <is>
-          <t>Открылась анкета «Создание клиента»</t>
+          <t>Предусловие 2</t>
+        </is>
+      </c>
+      <c r="F206" s="2" t="inlineStr">
+        <is>
+          <t>Подготовлены данные человека, которого нет в ЕФР и в списках финмониторинга</t>
+        </is>
+      </c>
+      <c r="J206" s="2" t="inlineStr">
+        <is>
+          <t>Гусев Роман Ильич, 14.02.1979, пол мужской; паспорт 4518 700701, выдан 03.03.2024, код подразделения 770-045, ГУ МВД России по г. Москве; телефон +7 900 222-33-44; адрес: г. Москва, ул. Тестовая, д. 5, кв. 12</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="E207" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G207" s="2" t="inlineStr">
         <is>
-          <t>Заполнить анкету данными из предусловия 2 и нажать «Сохранить»</t>
+          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
         </is>
       </c>
       <c r="I207" s="2" t="inlineStr">
         <is>
-          <t>Открылось окно «Обратите внимание» с текстом «Выявлено совпадение данных клиента со следующими списками: Решения межведомственной комиссии. Информация будет передана в финмониторинг.»</t>
+          <t>Открылась анкета «Создание клиента»</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="E208" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G208" s="2" t="inlineStr">
         <is>
-          <t>Проверить кнопки в окне</t>
+          <t>Заполнить анкету данными из предусловия 2 и нажать «Сохранить»</t>
         </is>
       </c>
       <c r="I208" s="2" t="inlineStr">
         <is>
-          <t>В окне доступна кнопка «Ок»</t>
+          <t>Открылось окно «Обратите внимание» с текстом «Выявлено совпадение данных клиента со следующими списками: Решения межведомственной комиссии. Информация будет передана в финмониторинг.»</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="E209" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G209" s="2" t="inlineStr">
         <is>
-          <t>Проверить ответ сервиса CheckPerson в логах</t>
+          <t>Проверить кнопки в окне</t>
         </is>
       </c>
       <c r="I209" s="2" t="inlineStr">
         <is>
-          <t>В ответе сервиса есть признак совпадения со списком «Решения межведомственной комиссии»</t>
+          <t>В окне доступна кнопка «Ок»</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="E210" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G210" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Ок»</t>
+          <t>Проверить ответ сервиса CheckPerson в логах</t>
         </is>
       </c>
       <c r="I210" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Карточка клиента сохранена», клиент в статусе «Активен», подтверждение контролёром не требуется</t>
+          <t>В ответе сервиса есть признак совпадения со списком «Решения межведомственной комиссии»</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="E211" s="2" t="inlineStr">
         <is>
+          <t>Шаг 5</t>
+        </is>
+      </c>
+      <c r="G211" s="2" t="inlineStr">
+        <is>
+          <t>Нажать «Ок»</t>
+        </is>
+      </c>
+      <c r="I211" s="2" t="inlineStr">
+        <is>
+          <t>Выводится сообщение «Карточка клиента сохранена», клиент в статусе «Активен», подтверждение контролёром не требуется</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="E212" s="2" t="inlineStr">
+        <is>
           <t>Шаг 6</t>
         </is>
       </c>
-      <c r="G211" s="2" t="inlineStr">
+      <c r="G212" s="2" t="inlineStr">
         <is>
           <t>Открыть карточку клиента, вкладку «История операций»</t>
         </is>
       </c>
-      <c r="I211" s="2" t="inlineStr">
+      <c r="I212" s="2" t="inlineStr">
         <is>
           <t>Информация передана в финмониторинг</t>
         </is>
       </c>
     </row>
-    <row r="212">
-      <c r="A212" s="2" t="inlineStr">
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
         <is>
           <t>900418</t>
         </is>
       </c>
-      <c r="B212" s="2" t="inlineStr">
+      <c r="B213" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Анкета</t>
         </is>
       </c>
-      <c r="C212" s="2" t="inlineStr">
+      <c r="C213" s="2" t="inlineStr">
         <is>
           <t>Создание клиента: граница возраста 14 лет — младше отказ, в день 14-летия создание</t>
         </is>
       </c>
-      <c r="D212" s="2" t="inlineStr">
+      <c r="D213" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M212" s="2" t="inlineStr">
+      <c r="M213" s="2" t="inlineStr">
         <is>
           <t>Высокий</t>
         </is>
       </c>
-      <c r="N212" s="2" t="inlineStr">
+      <c r="N213" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O212" s="2" t="inlineStr">
+      <c r="O213" s="2" t="inlineStr">
         <is>
           <t>9/29/2026 16:12:58</t>
         </is>
       </c>
-      <c r="P212" s="2" t="inlineStr">
+      <c r="P213" s="2" t="inlineStr">
         <is>
           <t>Владимир Астахов</t>
         </is>
       </c>
-      <c r="Q212" s="2" t="inlineStr">
+      <c r="Q213" s="2" t="inlineStr">
         <is>
           <t>biq90103, client, age</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="E213" s="2" t="inlineStr">
-        <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F213" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
-        </is>
-      </c>
-      <c r="I213" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J213" s="2" t="inlineStr">
-        <is>
-          <t>tst_oper01</t>
-        </is>
-      </c>
-      <c r="K213" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="E214" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G214" s="2" t="inlineStr">
-        <is>
-          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
+          <t>Предусловие 1</t>
+        </is>
+      </c>
+      <c r="F214" s="2" t="inlineStr">
+        <is>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
         </is>
       </c>
       <c r="I214" s="2" t="inlineStr">
         <is>
-          <t>Открылась анкета «Создание клиента»</t>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J214" s="2" t="inlineStr">
+        <is>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K214" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="E215" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G215" s="2" t="inlineStr">
         <is>
-          <t>Заполнить обязательные поля анкеты, кроме даты рождения</t>
+          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
         </is>
       </c>
       <c r="I215" s="2" t="inlineStr">
         <is>
-          <t>Поля анкеты заполнены</t>
+          <t>Открылась анкета «Создание клиента»</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="E216" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G216" s="2" t="inlineStr">
         <is>
-          <t>В поле «Дата рождения» ввести дату, при которой клиенту меньше 14 лет</t>
+          <t>Заполнить обязательные поля анкеты, кроме даты рождения</t>
         </is>
       </c>
       <c r="I216" s="2" t="inlineStr">
         <is>
-          <t>Дата отображается в поле</t>
-        </is>
-      </c>
-      <c r="J216" s="2" t="inlineStr">
-        <is>
-          <t>10.05.2015</t>
+          <t>Поля анкеты заполнены</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="E217" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G217" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Сохранить»</t>
+          <t>В поле «Дата рождения» ввести дату, при которой клиенту меньше 14 лет</t>
         </is>
       </c>
       <c r="I217" s="2" t="inlineStr">
         <is>
-          <t>Кнопка «Сохранить» неактивна, анкета не сохраняется</t>
+          <t>Дата отображается в поле</t>
+        </is>
+      </c>
+      <c r="J217" s="2" t="inlineStr">
+        <is>
+          <t>10.05.2015</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="E218" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G218" s="2" t="inlineStr">
         <is>
-          <t>Изменить дату рождения так, чтобы клиенту сегодня исполнилось 14 лет</t>
+          <t>Нажать «Сохранить»</t>
         </is>
       </c>
       <c r="I218" s="2" t="inlineStr">
         <is>
-          <t>Дата отображается в поле</t>
-        </is>
-      </c>
-      <c r="J218" s="2" t="inlineStr">
-        <is>
-          <t>Сегодняшняя дата 14 лет назад</t>
+          <t>Кнопка «Сохранить» неактивна, анкета не сохраняется</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="E219" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G219" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Сохранить»</t>
+          <t>Изменить дату рождения так, чтобы клиенту сегодня исполнилось 14 лет</t>
         </is>
       </c>
       <c r="I219" s="2" t="inlineStr">
         <is>
-          <t>Выводится окно «Обратите внимание» с текстом «Клиенту исполнилось 14 лет», затем сообщение «Карточка клиента сохранена»</t>
+          <t>Дата отображается в поле</t>
+        </is>
+      </c>
+      <c r="J219" s="2" t="inlineStr">
+        <is>
+          <t>Сегодняшняя дата 14 лет назад</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="E220" s="2" t="inlineStr">
         <is>
+          <t>Шаг 6</t>
+        </is>
+      </c>
+      <c r="G220" s="2" t="inlineStr">
+        <is>
+          <t>Нажать «Сохранить»</t>
+        </is>
+      </c>
+      <c r="I220" s="2" t="inlineStr">
+        <is>
+          <t>Выводится окно «Обратите внимание» с текстом «Клиенту исполнилось 14 лет», затем сообщение «Карточка клиента сохранена»</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="E221" s="2" t="inlineStr">
+        <is>
           <t>Шаг 7</t>
         </is>
       </c>
-      <c r="G220" s="2" t="inlineStr">
+      <c r="G221" s="2" t="inlineStr">
         <is>
           <t>Выполнить поиск клиента по паспорту из анкеты</t>
         </is>
       </c>
-      <c r="I220" s="2" t="inlineStr">
+      <c r="I221" s="2" t="inlineStr">
         <is>
           <t>Клиент создан корректно</t>
         </is>
       </c>
     </row>
-    <row r="221">
-      <c r="A221" s="2" t="inlineStr">
+    <row r="222">
+      <c r="A222" s="2" t="inlineStr">
         <is>
           <t>900419</t>
         </is>
       </c>
-      <c r="B221" s="2" t="inlineStr">
+      <c r="B222" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Проверка на дубль</t>
         </is>
       </c>
-      <c r="C221" s="2" t="inlineStr">
+      <c r="C222" s="2" t="inlineStr">
         <is>
           <t>Создание клиента: дубль по паспорту</t>
         </is>
       </c>
-      <c r="D221" s="2" t="inlineStr">
+      <c r="D222" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M221" s="2" t="inlineStr">
+      <c r="M222" s="2" t="inlineStr">
         <is>
           <t>Самый высокий</t>
         </is>
       </c>
-      <c r="N221" s="2" t="inlineStr">
+      <c r="N222" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O221" s="2" t="inlineStr">
+      <c r="O222" s="2" t="inlineStr">
         <is>
           <t>9/30/2026 09:47:13</t>
         </is>
       </c>
-      <c r="P221" s="2" t="inlineStr">
+      <c r="P222" s="2" t="inlineStr">
         <is>
           <t>Дарья Мельникова</t>
         </is>
       </c>
-      <c r="Q221" s="2" t="inlineStr">
+      <c r="Q222" s="2" t="inlineStr">
         <is>
           <t>biq90103, client, duplicate, negative</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="E222" s="2" t="inlineStr">
-        <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F222" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
-        </is>
-      </c>
-      <c r="I222" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J222" s="2" t="inlineStr">
-        <is>
-          <t>tst_kmtp01</t>
-        </is>
-      </c>
-      <c r="K222" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900903 «Вход в ЕФР в роли клиентского менеджера»</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="E223" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
+          <t>Предусловие 1</t>
         </is>
       </c>
       <c r="F223" s="2" t="inlineStr">
         <is>
-          <t>В ЕФР есть клиент Лосева Инна Павловна, 30.09.1988, паспорт 4510 555777</t>
+          <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
+        </is>
+      </c>
+      <c r="I223" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J223" s="2" t="inlineStr">
+        <is>
+          <t>tst_kmtp01</t>
+        </is>
+      </c>
+      <c r="K223" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900903 «Вход в ЕФР в роли клиентского менеджера»</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="E224" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 3</t>
+          <t>Предусловие 2</t>
         </is>
       </c>
       <c r="F224" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
-        </is>
-      </c>
-      <c r="I224" s="2" t="inlineStr">
-        <is>
-          <t>Открылась анкета «Создание клиента»</t>
+          <t>В ЕФР есть клиент Лосева Инна Павловна, 30.09.1988, паспорт 4510 555777</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="E225" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G225" s="2" t="inlineStr">
-        <is>
-          <t>Заполнить анкету: ФИО и дата рождения — другие, паспорт — клиента из предусловия 2</t>
+          <t>Предусловие 3</t>
+        </is>
+      </c>
+      <c r="F225" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» нажать «Создать клиента»</t>
         </is>
       </c>
       <c r="I225" s="2" t="inlineStr">
         <is>
-          <t>В анкете заполнены все обязательные поля</t>
-        </is>
-      </c>
-      <c r="J225" s="2" t="inlineStr">
-        <is>
-          <t>Лосев Артём Викторович, 17.01.1991, пол мужской; паспорт 4510 555778, выдан 22.04.2023, код подразделения 500-031, ГУ МВД России по Московской обл.; телефон +7 900 333-44-55; адрес: г. Москва, ул. Тестовая, д. 9, кв. 3</t>
+          <t>Открылась анкета «Создание клиента»</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="E226" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G226" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Сохранить»</t>
+          <t>В поле «Гражданство» выбрать «РФ». Заполнить анкету: ФИО и дата рождения — другие, паспорт — клиента из предусловия 2</t>
         </is>
       </c>
       <c r="I226" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Найден клиент с этим паспортом. Обновите паспорт в карточке существующего клиента.» и кнопка «Открыть карточку»</t>
+          <t>В анкете заполнены все обязательные поля</t>
+        </is>
+      </c>
+      <c r="J226" s="2" t="inlineStr">
+        <is>
+          <t>Лосев Артём Викторович, 17.01.1991, пол мужской; паспорт 4510 555778, выдан 22.04.2023, код подразделения 500-031, ГУ МВД России по Московской обл.; телефон +7 900 333-44-55; адрес: г. Москва, ул. Тестовая, д. 9, кв. 3</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="E227" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G227" s="2" t="inlineStr">
         <is>
-          <t>Закрыть сообщение и повторно нажать «Сохранить»</t>
+          <t>Нажать «Сохранить»</t>
         </is>
       </c>
       <c r="I227" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Карточка клиента сохранена», карточка в статусе «Черновик»</t>
+          <t>Выводится сообщение «Найден клиент с этим паспортом. Обновите паспорт в карточке существующего клиента.» и кнопка «Открыть карточку»</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="E228" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G228" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Открыть карточку»</t>
+          <t>Закрыть сообщение и повторно нажать «Сохранить»</t>
+        </is>
+      </c>
+      <c r="I228" s="2" t="inlineStr">
+        <is>
+          <t>Выводится сообщение «Карточка клиента сохранена», карточка в статусе «Черновик»</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="E229" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G229" s="2" t="inlineStr">
         <is>
-          <t>На странице «Поиск клиента» выполнить поиск по паспорту 4510 555777</t>
-        </is>
-      </c>
-      <c r="I229" s="2" t="inlineStr">
-        <is>
-          <t>Найден один клиент</t>
+          <t>Нажать «Открыть карточку»</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="E230" s="2" t="inlineStr">
         <is>
+          <t>Шаг 5</t>
+        </is>
+      </c>
+      <c r="G230" s="2" t="inlineStr">
+        <is>
+          <t>На странице «Поиск клиента» выполнить поиск по паспорту 4510 555777</t>
+        </is>
+      </c>
+      <c r="I230" s="2" t="inlineStr">
+        <is>
+          <t>Найден один клиент</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="E231" s="2" t="inlineStr">
+        <is>
           <t>Шаг 6</t>
         </is>
       </c>
-      <c r="G230" s="2" t="inlineStr">
+      <c r="G231" s="2" t="inlineStr">
         <is>
           <t>Открыть карточку найденного клиента</t>
         </is>
       </c>
-      <c r="I230" s="2" t="inlineStr">
+      <c r="I231" s="2" t="inlineStr">
         <is>
           <t>ФИО, дата рождения и паспорт — клиента из предусловия 2: Лосева Инна Павловна, 30.09.1988, 4510 555777</t>
         </is>
       </c>
     </row>
-    <row r="231">
-      <c r="A231" s="2" t="inlineStr">
+    <row r="232">
+      <c r="A232" s="2" t="inlineStr">
         <is>
           <t>900420</t>
         </is>
       </c>
-      <c r="B231" s="2" t="inlineStr">
+      <c r="B232" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; РТ_Тест-кейсы_функциональные -&gt; 8. Клиенты -&gt; 8.3 BIQ-90103 Создание клиента -&gt; Проверка на дубль</t>
         </is>
       </c>
-      <c r="C231" s="2" t="inlineStr">
+      <c r="C232" s="2" t="inlineStr">
         <is>
           <t>Создание клиента: дубль без предыдущего паспорта и совпадение со списком — контролёр отменяет создание</t>
         </is>
       </c>
-      <c r="D231" s="2" t="inlineStr">
+      <c r="D232" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M231" s="2" t="inlineStr">
+      <c r="M232" s="2" t="inlineStr">
         <is>
           <t>Высокий</t>
         </is>
       </c>
-      <c r="N231" s="2" t="inlineStr">
+      <c r="N232" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O231" s="2" t="inlineStr">
+      <c r="O232" s="2" t="inlineStr">
         <is>
           <t>10/01/2026 13:25:39</t>
         </is>
       </c>
-      <c r="P231" s="2" t="inlineStr">
+      <c r="P232" s="2" t="inlineStr">
         <is>
           <t>Владимир Астахов</t>
         </is>
       </c>
-      <c r="Q231" s="2" t="inlineStr">
+      <c r="Q232" s="2" t="inlineStr">
         <is>
           <t>biq90103, client, duplicate, finmon, control</t>
-        </is>
-      </c>
-    </row>
-    <row r="232">
-      <c r="E232" s="2" t="inlineStr">
-        <is>
-          <t>Предусловие 1</t>
-        </is>
-      </c>
-      <c r="F232" s="2" t="inlineStr">
-        <is>
-          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
-        </is>
-      </c>
-      <c r="I232" s="2" t="inlineStr">
-        <is>
-          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
-        </is>
-      </c>
-      <c r="J232" s="2" t="inlineStr">
-        <is>
-          <t>tst_oper01</t>
-        </is>
-      </c>
-      <c r="K232" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="E233" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 2</t>
+          <t>Предусловие 1</t>
         </is>
       </c>
       <c r="F233" s="2" t="inlineStr">
         <is>
-          <t>Существующий клиент — клиент, созданный в кейсе 900415</t>
+          <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
+        </is>
+      </c>
+      <c r="I233" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
+        </is>
+      </c>
+      <c r="J233" s="2" t="inlineStr">
+        <is>
+          <t>tst_oper01</t>
+        </is>
+      </c>
+      <c r="K233" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900901 «Вход в ЕФР в роли менеджера-операциониста»</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="E234" s="2" t="inlineStr">
         <is>
-          <t>Предусловие 3</t>
+          <t>Предусловие 2</t>
         </is>
       </c>
       <c r="F234" s="2" t="inlineStr">
         <is>
-          <t>Данные нового человека: ФИО и дата рождения — как у существующего клиента, паспорт другой. Человек входит в список «Решения межведомственной комиссии»</t>
-        </is>
-      </c>
-      <c r="J234" s="2" t="inlineStr">
-        <is>
-          <t>Паспорт 4524 600602, выдан 15.06.2026, код подразделения 500-118, ГУ МВД России по Московской обл.; телефон +7 900 444-55-66; адрес: г. Москва, ул. Тестовая, д. 14, кв. 7</t>
+          <t>Существующий клиент — клиент, созданный в кейсе 900415</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="E235" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G235" s="2" t="inlineStr">
-        <is>
-          <t>Нажать «Создать клиента», заполнить анкету данными из предусловия 3 и нажать «Сохранить»</t>
-        </is>
-      </c>
-      <c r="I235" s="2" t="inlineStr">
-        <is>
-          <t>Открылось окно «Обратите внимание» с текстом «Клиент с такими ФИО и датой рождения уже есть в системе. Укажите данные предыдущего паспорта РФ, чтобы не создать дубль карточки.» и кнопками «Ввести данные предыдущего паспорта» и «Нет предыдущего паспорта»</t>
+          <t>Предусловие 3</t>
+        </is>
+      </c>
+      <c r="F235" s="2" t="inlineStr">
+        <is>
+          <t>Данные нового человека: ФИО и дата рождения — как у существующего клиента, паспорт другой. Человек входит в список «Решения межведомственной комиссии»</t>
+        </is>
+      </c>
+      <c r="J235" s="2" t="inlineStr">
+        <is>
+          <t>Пол женский; паспорт 4524 600602, выдан 15.06.2026, код подразделения 500-118, ГУ МВД России по Московской обл.; телефон +7 900 444-55-66; адрес: г. Москва, ул. Тестовая, д. 14, кв. 7</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="E236" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2</t>
+          <t>Шаг 1</t>
         </is>
       </c>
       <c r="G236" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Нет предыдущего паспорта»</t>
+          <t>Нажать «Создать клиента», заполнить анкету данными из предусловия 3 и нажать «Сохранить»</t>
         </is>
       </c>
       <c r="I236" s="2" t="inlineStr">
         <is>
-          <t>Выводится сообщение «Операция требует подтверждения контролирующим работником», заявка в статусе «На подтверждении»</t>
+          <t>Открылось окно «Обратите внимание» с текстом «Клиент с такими ФИО и датой рождения уже есть в системе. Укажите данные предыдущего паспорта РФ, чтобы не создать дубль карточки.» и кнопками «Ввести данные предыдущего паспорта» и «Нет предыдущего паспорта»</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="E237" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3</t>
+          <t>Шаг 2</t>
         </is>
       </c>
       <c r="G237" s="2" t="inlineStr">
         <is>
-          <t>Проверить передачу сведений в финмониторинг</t>
+          <t>Нажать «Нет предыдущего паспорта»</t>
         </is>
       </c>
       <c r="I237" s="2" t="inlineStr">
         <is>
-          <t>Сведения переданы в финмониторинг</t>
+          <t>Выводится сообщение «Операция требует подтверждения контролирующим работником», заявка в статусе «На подтверждении»</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="E238" s="2" t="inlineStr">
         <is>
-          <t>Шаг 4</t>
+          <t>Шаг 3</t>
         </is>
       </c>
       <c r="G238" s="2" t="inlineStr">
         <is>
-          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
+          <t>Проверить передачу сведений в финмониторинг</t>
         </is>
       </c>
       <c r="I238" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница входа в ЕФР</t>
-        </is>
-      </c>
-      <c r="K238" s="2" t="inlineStr">
-        <is>
-          <t>Общий шаг 900906 «Выход из ЕФР»</t>
+          <t>Сведения переданы в финмониторинг</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="E239" s="2" t="inlineStr">
         <is>
-          <t>Шаг 5</t>
+          <t>Шаг 4</t>
         </is>
       </c>
       <c r="G239" s="2" t="inlineStr">
         <is>
-          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+          <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
         </is>
       </c>
       <c r="I239" s="2" t="inlineStr">
         <is>
-          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
-        </is>
-      </c>
-      <c r="J239" s="2" t="inlineStr">
-        <is>
-          <t>tst_contr01</t>
+          <t>Открылась страница входа в ЕФР</t>
         </is>
       </c>
       <c r="K239" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
+          <t>Общий шаг 900906 «Выход из ЕФР»</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="E240" s="2" t="inlineStr">
         <is>
-          <t>Шаг 6</t>
+          <t>Шаг 5</t>
         </is>
       </c>
       <c r="G240" s="2" t="inlineStr">
         <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
+          <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
+        </is>
+      </c>
+      <c r="I240" s="2" t="inlineStr">
+        <is>
+          <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
+        </is>
+      </c>
+      <c r="J240" s="2" t="inlineStr">
+        <is>
+          <t>tst_contr01</t>
         </is>
       </c>
       <c r="K240" s="2" t="inlineStr">
         <is>
-          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
+          <t>Общий шаг 900904 «Вход в роли контролёра»</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="E241" s="2" t="inlineStr">
         <is>
-          <t>Шаг 7</t>
+          <t>Шаг 6</t>
         </is>
       </c>
       <c r="G241" s="2" t="inlineStr">
         <is>
-          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
-        </is>
-      </c>
-      <c r="I241" s="2" t="inlineStr">
-        <is>
-          <t>Открылась форма заявки в статусе «На подтверждении»</t>
+          <t>Нажать ссылку «Задачи» в хедере</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
@@ -5642,494 +5637,516 @@
     <row r="242">
       <c r="E242" s="2" t="inlineStr">
         <is>
-          <t>Шаг 8</t>
+          <t>Шаг 7</t>
         </is>
       </c>
       <c r="G242" s="2" t="inlineStr">
         <is>
-          <t>Проверить блок «Внимание» на форме заявки</t>
+          <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
         </is>
       </c>
       <c r="I242" s="2" t="inlineStr">
         <is>
-          <t>Выводится уведомление «Возможен дубль клиента. Проверьте данные в АБС перед подтверждением.» и данные найденного клиента: ФИО, дата рождения, паспорт</t>
+          <t>Открылась форма заявки в статусе «На подтверждении»</t>
+        </is>
+      </c>
+      <c r="K242" s="2" t="inlineStr">
+        <is>
+          <t>Общий шаг 900907 «Открытие заявки контролёром»</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="E243" s="2" t="inlineStr">
         <is>
-          <t>Шаг 9</t>
+          <t>Шаг 8</t>
         </is>
       </c>
       <c r="G243" s="2" t="inlineStr">
         <is>
-          <t>Нажать «Отменить операцию»</t>
+          <t>Проверить блок «Внимание» на форме заявки</t>
         </is>
       </c>
       <c r="I243" s="2" t="inlineStr">
         <is>
-          <t>Заявка отменена</t>
+          <t>Выводится уведомление «Возможен дубль клиента. Проверьте данные в АБС перед подтверждением.» и данные найденного клиента: ФИО, дата рождения, паспорт</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="E244" s="2" t="inlineStr">
         <is>
+          <t>Шаг 9</t>
+        </is>
+      </c>
+      <c r="G244" s="2" t="inlineStr">
+        <is>
+          <t>Нажать «Отменить операцию»</t>
+        </is>
+      </c>
+      <c r="I244" s="2" t="inlineStr">
+        <is>
+          <t>Заявка отменена</t>
+        </is>
+      </c>
+    </row>
+    <row r="245">
+      <c r="E245" s="2" t="inlineStr">
+        <is>
           <t>Шаг 10</t>
         </is>
       </c>
-      <c r="G244" s="2" t="inlineStr">
+      <c r="G245" s="2" t="inlineStr">
         <is>
           <t>Проверить статус заявки</t>
         </is>
       </c>
-      <c r="I244" s="2" t="inlineStr">
+      <c r="I245" s="2" t="inlineStr">
         <is>
           <t>Заявка в статусе «Отклонена», карточка клиента удалена</t>
         </is>
       </c>
     </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
+    <row r="246">
+      <c r="A246" s="2" t="inlineStr">
         <is>
           <t>900901</t>
         </is>
       </c>
-      <c r="B245" s="2" t="inlineStr">
+      <c r="B246" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; Общие шаги</t>
         </is>
       </c>
-      <c r="C245" s="2" t="inlineStr">
+      <c r="C246" s="2" t="inlineStr">
         <is>
           <t>Вход в ЕФР в роли менеджера-операциониста</t>
         </is>
       </c>
-      <c r="D245" s="2" t="inlineStr">
+      <c r="D246" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M245" s="2" t="inlineStr">
+      <c r="M246" s="2" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="N245" s="2" t="inlineStr">
+      <c r="N246" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O245" s="2" t="inlineStr">
+      <c r="O246" s="2" t="inlineStr">
         <is>
           <t>3/11/2025 09:40:12</t>
         </is>
       </c>
-      <c r="P245" s="2" t="inlineStr">
+      <c r="P246" s="2" t="inlineStr">
         <is>
           <t>Максим Гаврилин</t>
         </is>
       </c>
     </row>
-    <row r="246">
-      <c r="E246" s="2" t="inlineStr">
+    <row r="247">
+      <c r="E247" s="2" t="inlineStr">
         <is>
           <t>Шаг 1</t>
         </is>
       </c>
-      <c r="G246" s="2" t="inlineStr">
+      <c r="G247" s="2" t="inlineStr">
         <is>
           <t>Выполнить вход в ЕФР в роли менеджера-операциониста ТП</t>
         </is>
       </c>
-      <c r="I246" s="2" t="inlineStr">
+      <c r="I247" s="2" t="inlineStr">
         <is>
           <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
         </is>
       </c>
-      <c r="J246" s="2" t="inlineStr">
+      <c r="J247" s="2" t="inlineStr">
         <is>
           <t>tst_oper01</t>
         </is>
       </c>
     </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
+    <row r="248">
+      <c r="A248" s="2" t="inlineStr">
         <is>
           <t>900902</t>
         </is>
       </c>
-      <c r="B247" s="2" t="inlineStr">
+      <c r="B248" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; Общие шаги</t>
         </is>
       </c>
-      <c r="C247" s="2" t="inlineStr">
+      <c r="C248" s="2" t="inlineStr">
         <is>
           <t>Вход в ЕФР в роли финансового консультанта</t>
         </is>
       </c>
-      <c r="D247" s="2" t="inlineStr">
+      <c r="D248" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M247" s="2" t="inlineStr">
+      <c r="M248" s="2" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="N247" s="2" t="inlineStr">
+      <c r="N248" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O247" s="2" t="inlineStr">
+      <c r="O248" s="2" t="inlineStr">
         <is>
           <t>3/11/2025 09:44:37</t>
         </is>
       </c>
-      <c r="P247" s="2" t="inlineStr">
+      <c r="P248" s="2" t="inlineStr">
         <is>
           <t>Максим Гаврилин</t>
         </is>
       </c>
     </row>
-    <row r="248">
-      <c r="E248" s="2" t="inlineStr">
+    <row r="249">
+      <c r="E249" s="2" t="inlineStr">
         <is>
           <t>Шаг 1</t>
         </is>
       </c>
-      <c r="G248" s="2" t="inlineStr">
+      <c r="G249" s="2" t="inlineStr">
         <is>
           <t>Выполнить вход в ЕФР в роли финансового консультанта ТП</t>
         </is>
       </c>
-      <c r="I248" s="2" t="inlineStr">
+      <c r="I249" s="2" t="inlineStr">
         <is>
           <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
         </is>
       </c>
-      <c r="J248" s="2" t="inlineStr">
+      <c r="J249" s="2" t="inlineStr">
         <is>
           <t>tst_fk01</t>
         </is>
       </c>
     </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
+    <row r="250">
+      <c r="A250" s="2" t="inlineStr">
         <is>
           <t>900903</t>
         </is>
       </c>
-      <c r="B249" s="2" t="inlineStr">
+      <c r="B250" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; Общие шаги</t>
         </is>
       </c>
-      <c r="C249" s="2" t="inlineStr">
+      <c r="C250" s="2" t="inlineStr">
         <is>
           <t>Вход в ЕФР в роли клиентского менеджера</t>
         </is>
       </c>
-      <c r="D249" s="2" t="inlineStr">
+      <c r="D250" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M249" s="2" t="inlineStr">
+      <c r="M250" s="2" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="N249" s="2" t="inlineStr">
+      <c r="N250" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O249" s="2" t="inlineStr">
+      <c r="O250" s="2" t="inlineStr">
         <is>
           <t>3/11/2025 09:47:05</t>
         </is>
       </c>
-      <c r="P249" s="2" t="inlineStr">
+      <c r="P250" s="2" t="inlineStr">
         <is>
           <t>Максим Гаврилин</t>
         </is>
       </c>
     </row>
-    <row r="250">
-      <c r="E250" s="2" t="inlineStr">
+    <row r="251">
+      <c r="E251" s="2" t="inlineStr">
         <is>
           <t>Шаг 1</t>
         </is>
       </c>
-      <c r="G250" s="2" t="inlineStr">
+      <c r="G251" s="2" t="inlineStr">
         <is>
           <t>Выполнить вход в ЕФР в роли клиентского менеджера ТП</t>
         </is>
       </c>
-      <c r="I250" s="2" t="inlineStr">
+      <c r="I251" s="2" t="inlineStr">
         <is>
           <t>Открылась страница «Поиск клиента», в хедере отображаются ФИО и роль пользователя</t>
         </is>
       </c>
-      <c r="J250" s="2" t="inlineStr">
+      <c r="J251" s="2" t="inlineStr">
         <is>
           <t>tst_kmtp01</t>
         </is>
       </c>
     </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
+    <row r="252">
+      <c r="A252" s="2" t="inlineStr">
         <is>
           <t>900904</t>
         </is>
       </c>
-      <c r="B251" s="2" t="inlineStr">
+      <c r="B252" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; Общие шаги</t>
         </is>
       </c>
-      <c r="C251" s="2" t="inlineStr">
+      <c r="C252" s="2" t="inlineStr">
         <is>
           <t>Вход в роли контролёра</t>
         </is>
       </c>
-      <c r="D251" s="2" t="inlineStr">
+      <c r="D252" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M251" s="2" t="inlineStr">
+      <c r="M252" s="2" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="N251" s="2" t="inlineStr">
+      <c r="N252" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O251" s="2" t="inlineStr">
+      <c r="O252" s="2" t="inlineStr">
         <is>
           <t>3/11/2025 09:52:19</t>
         </is>
       </c>
-      <c r="P251" s="2" t="inlineStr">
+      <c r="P252" s="2" t="inlineStr">
         <is>
           <t>Максим Гаврилин</t>
         </is>
       </c>
     </row>
-    <row r="252">
-      <c r="E252" s="2" t="inlineStr">
+    <row r="253">
+      <c r="E253" s="2" t="inlineStr">
         <is>
           <t>Шаг 1</t>
         </is>
       </c>
-      <c r="G252" s="2" t="inlineStr">
+      <c r="G253" s="2" t="inlineStr">
         <is>
           <t>Выполнить вход в ЕФР в роли контролёра ТП того же филиала, что и сотрудник, оформивший заявку</t>
         </is>
       </c>
-      <c r="I252" s="2" t="inlineStr">
+      <c r="I253" s="2" t="inlineStr">
         <is>
           <t>Открылась страница, в хедере которой есть ссылка на раздел «Задачи»</t>
         </is>
       </c>
-      <c r="J252" s="2" t="inlineStr">
+      <c r="J253" s="2" t="inlineStr">
         <is>
           <t>tst_contr01</t>
         </is>
       </c>
     </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
+    <row r="254">
+      <c r="A254" s="2" t="inlineStr">
         <is>
           <t>900905</t>
         </is>
       </c>
-      <c r="B253" s="2" t="inlineStr">
+      <c r="B254" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; Общие шаги</t>
         </is>
       </c>
-      <c r="C253" s="2" t="inlineStr">
+      <c r="C254" s="2" t="inlineStr">
         <is>
           <t>Поиск клиента по паспорту</t>
         </is>
       </c>
-      <c r="D253" s="2" t="inlineStr">
+      <c r="D254" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M253" s="2" t="inlineStr">
+      <c r="M254" s="2" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="N253" s="2" t="inlineStr">
+      <c r="N254" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O253" s="2" t="inlineStr">
+      <c r="O254" s="2" t="inlineStr">
         <is>
           <t>3/12/2025 14:05:51</t>
         </is>
       </c>
-      <c r="P253" s="2" t="inlineStr">
+      <c r="P254" s="2" t="inlineStr">
         <is>
           <t>Людмила Жаркова</t>
         </is>
       </c>
     </row>
-    <row r="254">
-      <c r="E254" s="2" t="inlineStr">
+    <row r="255">
+      <c r="E255" s="2" t="inlineStr">
         <is>
           <t>Шаг 1</t>
         </is>
       </c>
-      <c r="G254" s="2" t="inlineStr">
+      <c r="G255" s="2" t="inlineStr">
         <is>
           <t>На странице «Поиск клиента» ввести серию и номер паспорта клиента из предусловий и нажать «Найти»</t>
         </is>
       </c>
-      <c r="I254" s="2" t="inlineStr">
+      <c r="I255" s="2" t="inlineStr">
         <is>
           <t>Клиент найден, открылся продуктовый профиль клиента с его ФИО и паспортом</t>
         </is>
       </c>
     </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
+    <row r="256">
+      <c r="A256" s="2" t="inlineStr">
         <is>
           <t>900906</t>
         </is>
       </c>
-      <c r="B255" s="2" t="inlineStr">
+      <c r="B256" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; Общие шаги</t>
         </is>
       </c>
-      <c r="C255" s="2" t="inlineStr">
+      <c r="C256" s="2" t="inlineStr">
         <is>
           <t>Выход из ЕФР</t>
         </is>
       </c>
-      <c r="D255" s="2" t="inlineStr">
+      <c r="D256" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M255" s="2" t="inlineStr">
+      <c r="M256" s="2" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="N255" s="2" t="inlineStr">
+      <c r="N256" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O255" s="2" t="inlineStr">
+      <c r="O256" s="2" t="inlineStr">
         <is>
           <t>3/12/2025 14:11:26</t>
         </is>
       </c>
-      <c r="P255" s="2" t="inlineStr">
+      <c r="P256" s="2" t="inlineStr">
         <is>
           <t>Людмила Жаркова</t>
         </is>
       </c>
     </row>
-    <row r="256">
-      <c r="E256" s="2" t="inlineStr">
+    <row r="257">
+      <c r="E257" s="2" t="inlineStr">
         <is>
           <t>Шаг 1</t>
         </is>
       </c>
-      <c r="G256" s="2" t="inlineStr">
+      <c r="G257" s="2" t="inlineStr">
         <is>
           <t>Выйти из ЕФР нажатием ссылки «Выход»</t>
         </is>
       </c>
-      <c r="I256" s="2" t="inlineStr">
+      <c r="I257" s="2" t="inlineStr">
         <is>
           <t>Открылась страница входа в ЕФР</t>
         </is>
       </c>
     </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
+    <row r="258">
+      <c r="A258" s="2" t="inlineStr">
         <is>
           <t>900907</t>
         </is>
       </c>
-      <c r="B257" s="2" t="inlineStr">
+      <c r="B258" s="2" t="inlineStr">
         <is>
           <t>РТ_ЕФР -&gt; Общие шаги</t>
         </is>
       </c>
-      <c r="C257" s="2" t="inlineStr">
+      <c r="C258" s="2" t="inlineStr">
         <is>
           <t>Открытие заявки контролёром</t>
         </is>
       </c>
-      <c r="D257" s="2" t="inlineStr">
+      <c r="D258" s="2" t="inlineStr">
         <is>
           <t>Нет</t>
         </is>
       </c>
-      <c r="M257" s="2" t="inlineStr">
+      <c r="M258" s="2" t="inlineStr">
         <is>
           <t>Средний</t>
         </is>
       </c>
-      <c r="N257" s="2" t="inlineStr">
+      <c r="N258" s="2" t="inlineStr">
         <is>
           <t>Готов</t>
         </is>
       </c>
-      <c r="O257" s="2" t="inlineStr">
+      <c r="O258" s="2" t="inlineStr">
         <is>
           <t>8/04/2025 12:41:12</t>
         </is>
       </c>
-      <c r="P257" s="2" t="inlineStr">
+      <c r="P258" s="2" t="inlineStr">
         <is>
           <t>Максим Гаврилин</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="E258" s="2" t="inlineStr">
-        <is>
-          <t>Шаг 1</t>
-        </is>
-      </c>
-      <c r="G258" s="2" t="inlineStr">
-        <is>
-          <t>Нажать ссылку «Задачи» в хедере</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="E259" s="2" t="inlineStr">
         <is>
+          <t>Шаг 1</t>
+        </is>
+      </c>
+      <c r="G259" s="2" t="inlineStr">
+        <is>
+          <t>Нажать ссылку «Задачи» в хедере</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="E260" s="2" t="inlineStr">
+        <is>
           <t>Шаг 2</t>
         </is>
       </c>
-      <c r="G259" s="2" t="inlineStr">
+      <c r="G260" s="2" t="inlineStr">
         <is>
           <t>В списке «Все задачи» найти заявку по ФИО клиента и нажать «Взять и исполнить»</t>
         </is>
       </c>
-      <c r="I259" s="2" t="inlineStr">
+      <c r="I260" s="2" t="inlineStr">
         <is>
           <t>Открылась форма заявки в статусе «На подтверждении»</t>
         </is>
